--- a/packaging/release_templates/templates/forwarders/deshu_t3.xlsx
+++ b/packaging/release_templates/templates/forwarders/deshu_t3.xlsx
@@ -3523,7 +3523,7 @@
     <row r="21" ht="51" customFormat="1" customHeight="1" s="4">
       <c r="A21" s="46" t="inlineStr">
         <is>
-          <t>FBA22232AF13</t>
+          <t>FBATEST0DEMO</t>
         </is>
       </c>
       <c r="B21" s="46" t="inlineStr">
